--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121367308</v>
       </c>
       <c r="B2" t="n">
-        <v>97979</v>
+        <v>97989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368513</v>
+        <v>121368514</v>
       </c>
       <c r="B3" t="n">
-        <v>99110</v>
+        <v>99120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,17 +814,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R3" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368514</v>
+        <v>121371841</v>
       </c>
       <c r="B4" t="n">
-        <v>99110</v>
+        <v>108965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121364323</v>
+        <v>121366971</v>
       </c>
       <c r="B5" t="n">
-        <v>98744</v>
+        <v>98059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,25 +996,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121366035</v>
+        <v>121364323</v>
       </c>
       <c r="B6" t="n">
-        <v>98073</v>
+        <v>98754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,41 +1099,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R6" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S6" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121368982</v>
+        <v>121367305</v>
       </c>
       <c r="B7" t="n">
-        <v>105075</v>
+        <v>97989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1202,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R7" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121371841</v>
+        <v>121366035</v>
       </c>
       <c r="B8" t="n">
-        <v>108955</v>
+        <v>98083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121366971</v>
+        <v>121367281</v>
       </c>
       <c r="B9" t="n">
-        <v>98049</v>
+        <v>97991</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,37 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>223572</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R9" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367281</v>
+        <v>121368982</v>
       </c>
       <c r="B10" t="n">
-        <v>97981</v>
+        <v>105085</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223572</v>
+        <v>221137</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367305</v>
+        <v>121368513</v>
       </c>
       <c r="B11" t="n">
-        <v>97979</v>
+        <v>99120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
         <v>121366702</v>
       </c>
       <c r="B12" t="n">
-        <v>98056</v>
+        <v>98066</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121367308</v>
+        <v>121366702</v>
       </c>
       <c r="B2" t="n">
-        <v>97989</v>
+        <v>98066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219788</v>
+        <v>219799</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R2" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368514</v>
+        <v>121368982</v>
       </c>
       <c r="B3" t="n">
-        <v>99120</v>
+        <v>105085</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,20 +790,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222662</v>
+        <v>221137</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121366971</v>
+        <v>121364323</v>
       </c>
       <c r="B5" t="n">
-        <v>98059</v>
+        <v>98754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,25 +996,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121364323</v>
+        <v>121366971</v>
       </c>
       <c r="B6" t="n">
-        <v>98754</v>
+        <v>98059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121367305</v>
+        <v>121367308</v>
       </c>
       <c r="B7" t="n">
         <v>97989</v>
@@ -1226,17 +1226,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R7" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S7" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121366035</v>
+        <v>121367281</v>
       </c>
       <c r="B8" t="n">
-        <v>98083</v>
+        <v>97991</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,21 +1309,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>223572</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121367281</v>
+        <v>121367305</v>
       </c>
       <c r="B9" t="n">
-        <v>97991</v>
+        <v>97989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,37 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223572</v>
+        <v>219788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S9" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121368982</v>
+        <v>121366035</v>
       </c>
       <c r="B10" t="n">
-        <v>105085</v>
+        <v>98083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121366702</v>
+        <v>121368514</v>
       </c>
       <c r="B12" t="n">
-        <v>98066</v>
+        <v>99120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,37 +1721,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219799</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R12" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366702</v>
+        <v>121366971</v>
       </c>
       <c r="B2" t="n">
-        <v>98066</v>
+        <v>98072</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>121368982</v>
       </c>
       <c r="B3" t="n">
-        <v>105085</v>
+        <v>105098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121371841</v>
+        <v>121364323</v>
       </c>
       <c r="B4" t="n">
-        <v>108965</v>
+        <v>98767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R4" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +952,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121364323</v>
+        <v>121367305</v>
       </c>
       <c r="B5" t="n">
-        <v>98754</v>
+        <v>98002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,25 +996,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121366971</v>
+        <v>121367308</v>
       </c>
       <c r="B6" t="n">
-        <v>98059</v>
+        <v>98002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R6" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121367308</v>
+        <v>121366035</v>
       </c>
       <c r="B7" t="n">
-        <v>97989</v>
+        <v>98096</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121367281</v>
+        <v>121368513</v>
       </c>
       <c r="B8" t="n">
-        <v>97991</v>
+        <v>99133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,37 +1309,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223572</v>
+        <v>222662</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R8" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S8" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121367305</v>
+        <v>121368514</v>
       </c>
       <c r="B9" t="n">
-        <v>97989</v>
+        <v>99133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,37 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R9" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121366035</v>
+        <v>121367281</v>
       </c>
       <c r="B10" t="n">
-        <v>98083</v>
+        <v>98004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>223572</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121368513</v>
+        <v>121366702</v>
       </c>
       <c r="B11" t="n">
-        <v>99120</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222662</v>
+        <v>219799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121368514</v>
+        <v>121371841</v>
       </c>
       <c r="B12" t="n">
-        <v>99120</v>
+        <v>108978</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,20 +1717,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366971</v>
+        <v>121366035</v>
       </c>
       <c r="B2" t="n">
-        <v>98072</v>
+        <v>98097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R2" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368982</v>
+        <v>121366702</v>
       </c>
       <c r="B3" t="n">
-        <v>105098</v>
+        <v>98080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,41 +790,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R3" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121364323</v>
+        <v>121368514</v>
       </c>
       <c r="B4" t="n">
-        <v>98767</v>
+        <v>99134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,41 +893,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222322</v>
+        <v>222662</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R4" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +952,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367305</v>
+        <v>121366971</v>
       </c>
       <c r="B5" t="n">
-        <v>98002</v>
+        <v>98073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121367308</v>
+        <v>121368982</v>
       </c>
       <c r="B6" t="n">
-        <v>98002</v>
+        <v>105099</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121366035</v>
+        <v>121367281</v>
       </c>
       <c r="B7" t="n">
-        <v>98096</v>
+        <v>98005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121368513</v>
+        <v>121364323</v>
       </c>
       <c r="B8" t="n">
-        <v>99133</v>
+        <v>98768</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222662</v>
+        <v>222322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121368514</v>
+        <v>121367308</v>
       </c>
       <c r="B9" t="n">
-        <v>99133</v>
+        <v>98003</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367281</v>
+        <v>121371841</v>
       </c>
       <c r="B10" t="n">
-        <v>98004</v>
+        <v>108979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223572</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121366702</v>
+        <v>121368513</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>99134</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>222662</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121371841</v>
+        <v>121367305</v>
       </c>
       <c r="B12" t="n">
-        <v>108978</v>
+        <v>98003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1717,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R12" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S12" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366035</v>
+        <v>121366702</v>
       </c>
       <c r="B2" t="n">
-        <v>98097</v>
+        <v>98083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R2" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121366702</v>
+        <v>121368982</v>
       </c>
       <c r="B3" t="n">
-        <v>98080</v>
+        <v>105102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,41 +790,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R3" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368514</v>
+        <v>121368513</v>
       </c>
       <c r="B4" t="n">
-        <v>99134</v>
+        <v>99137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,17 +917,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R4" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +952,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121366971</v>
+        <v>121367308</v>
       </c>
       <c r="B5" t="n">
-        <v>98073</v>
+        <v>98006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R5" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368982</v>
+        <v>121371841</v>
       </c>
       <c r="B6" t="n">
-        <v>105099</v>
+        <v>108982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121367281</v>
+        <v>121366971</v>
       </c>
       <c r="B7" t="n">
-        <v>98005</v>
+        <v>98076</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R7" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121364323</v>
+        <v>121366035</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,41 +1305,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R8" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121367308</v>
+        <v>121367305</v>
       </c>
       <c r="B9" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,17 +1432,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S9" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121371841</v>
+        <v>121368514</v>
       </c>
       <c r="B10" t="n">
-        <v>108979</v>
+        <v>99137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,20 +1511,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121368513</v>
+        <v>121367281</v>
       </c>
       <c r="B11" t="n">
-        <v>99134</v>
+        <v>98008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,37 +1618,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222662</v>
+        <v>223572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R11" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S11" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367305</v>
+        <v>121364323</v>
       </c>
       <c r="B12" t="n">
-        <v>98003</v>
+        <v>98771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219788</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366702</v>
+        <v>121368982</v>
       </c>
       <c r="B2" t="n">
-        <v>98083</v>
+        <v>105102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R2" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368982</v>
+        <v>121368513</v>
       </c>
       <c r="B3" t="n">
-        <v>105102</v>
+        <v>99137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,20 +790,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221137</v>
+        <v>222662</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,17 +814,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R3" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368513</v>
+        <v>121367305</v>
       </c>
       <c r="B4" t="n">
-        <v>99137</v>
+        <v>98006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367308</v>
+        <v>121368514</v>
       </c>
       <c r="B5" t="n">
-        <v>98006</v>
+        <v>99137</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,12 +1055,12 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121371841</v>
+        <v>121367281</v>
       </c>
       <c r="B6" t="n">
-        <v>108982</v>
+        <v>98008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>223572</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121366971</v>
+        <v>121367308</v>
       </c>
       <c r="B7" t="n">
-        <v>98076</v>
+        <v>98006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R7" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S7" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121366035</v>
+        <v>121364323</v>
       </c>
       <c r="B8" t="n">
-        <v>98100</v>
+        <v>98771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,41 +1305,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R8" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S8" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121367305</v>
+        <v>121366971</v>
       </c>
       <c r="B9" t="n">
-        <v>98006</v>
+        <v>98076</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121368514</v>
+        <v>121366035</v>
       </c>
       <c r="B10" t="n">
-        <v>99137</v>
+        <v>98100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367281</v>
+        <v>121371841</v>
       </c>
       <c r="B11" t="n">
-        <v>98008</v>
+        <v>108982</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223572</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121364323</v>
+        <v>121366702</v>
       </c>
       <c r="B12" t="n">
-        <v>98771</v>
+        <v>98083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>219799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121368982</v>
+        <v>121366971</v>
       </c>
       <c r="B2" t="n">
-        <v>105102</v>
+        <v>98082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R2" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368513</v>
+        <v>121364323</v>
       </c>
       <c r="B3" t="n">
-        <v>99137</v>
+        <v>98777</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222662</v>
+        <v>222322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121367305</v>
+        <v>121368513</v>
       </c>
       <c r="B4" t="n">
-        <v>98006</v>
+        <v>99143</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121368514</v>
+        <v>121371841</v>
       </c>
       <c r="B5" t="n">
-        <v>99137</v>
+        <v>108988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,20 +996,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121367281</v>
+        <v>121366035</v>
       </c>
       <c r="B6" t="n">
-        <v>98008</v>
+        <v>98106</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223572</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121367308</v>
+        <v>121368514</v>
       </c>
       <c r="B7" t="n">
-        <v>98006</v>
+        <v>99143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121364323</v>
+        <v>121366702</v>
       </c>
       <c r="B8" t="n">
-        <v>98771</v>
+        <v>98089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>219799</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121366971</v>
+        <v>121367308</v>
       </c>
       <c r="B9" t="n">
-        <v>98076</v>
+        <v>98012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,37 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R9" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121366035</v>
+        <v>121368982</v>
       </c>
       <c r="B10" t="n">
-        <v>98100</v>
+        <v>105108</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121371841</v>
+        <v>121367281</v>
       </c>
       <c r="B11" t="n">
-        <v>108982</v>
+        <v>98014</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>223572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121366702</v>
+        <v>121367305</v>
       </c>
       <c r="B12" t="n">
-        <v>98083</v>
+        <v>98012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219799</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366971</v>
+        <v>121367281</v>
       </c>
       <c r="B2" t="n">
-        <v>98082</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>223572</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R2" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121364323</v>
+        <v>121367305</v>
       </c>
       <c r="B3" t="n">
-        <v>98777</v>
+        <v>98013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>219788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -884,7 +884,7 @@
         <v>121368513</v>
       </c>
       <c r="B4" t="n">
-        <v>99143</v>
+        <v>99144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121371841</v>
+        <v>121366035</v>
       </c>
       <c r="B5" t="n">
-        <v>108988</v>
+        <v>98107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,25 +996,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121366035</v>
+        <v>121368514</v>
       </c>
       <c r="B6" t="n">
-        <v>98106</v>
+        <v>99144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>222662</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121368514</v>
+        <v>121366702</v>
       </c>
       <c r="B7" t="n">
-        <v>99143</v>
+        <v>98090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222662</v>
+        <v>219799</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R7" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121366702</v>
+        <v>121364323</v>
       </c>
       <c r="B8" t="n">
-        <v>98089</v>
+        <v>98778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219799</v>
+        <v>222322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
         <v>121367308</v>
       </c>
       <c r="B9" t="n">
-        <v>98012</v>
+        <v>98013</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121368982</v>
+        <v>121366971</v>
       </c>
       <c r="B10" t="n">
-        <v>105108</v>
+        <v>98083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,41 +1511,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R10" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S10" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367281</v>
+        <v>121368982</v>
       </c>
       <c r="B11" t="n">
-        <v>98014</v>
+        <v>105109</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223572</v>
+        <v>221137</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367305</v>
+        <v>121371841</v>
       </c>
       <c r="B12" t="n">
-        <v>98012</v>
+        <v>108989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1717,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R12" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121367281</v>
+        <v>121367305</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223572</v>
+        <v>219788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R2" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121367305</v>
+        <v>121368513</v>
       </c>
       <c r="B3" t="n">
-        <v>98013</v>
+        <v>99144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -881,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368513</v>
+        <v>121368514</v>
       </c>
       <c r="B4" t="n">
         <v>99144</v>
@@ -917,17 +917,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R4" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +952,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121366035</v>
+        <v>121366702</v>
       </c>
       <c r="B5" t="n">
-        <v>98107</v>
+        <v>98090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R5" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S5" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121368514</v>
+        <v>121366971</v>
       </c>
       <c r="B6" t="n">
-        <v>99144</v>
+        <v>98083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222662</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R6" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S6" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121366702</v>
+        <v>121368982</v>
       </c>
       <c r="B7" t="n">
-        <v>98090</v>
+        <v>105109</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1202,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R7" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S7" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1261,12 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121364323</v>
+        <v>121366035</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,41 +1305,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R8" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121367308</v>
+        <v>121364323</v>
       </c>
       <c r="B9" t="n">
-        <v>98013</v>
+        <v>98778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,41 +1408,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219788</v>
+        <v>222322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S9" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1467,12 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121366971</v>
+        <v>121371841</v>
       </c>
       <c r="B10" t="n">
-        <v>98083</v>
+        <v>108989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,41 +1511,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R10" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S10" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121368982</v>
+        <v>121367281</v>
       </c>
       <c r="B11" t="n">
-        <v>105109</v>
+        <v>98015</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221137</v>
+        <v>223572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121371841</v>
+        <v>121367308</v>
       </c>
       <c r="B12" t="n">
-        <v>108989</v>
+        <v>98013</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121368513</v>
+        <v>121367308</v>
       </c>
       <c r="B3" t="n">
-        <v>99144</v>
+        <v>98013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R3" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121366702</v>
+        <v>121366035</v>
       </c>
       <c r="B5" t="n">
-        <v>98090</v>
+        <v>98107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R5" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121366971</v>
+        <v>121366702</v>
       </c>
       <c r="B6" t="n">
-        <v>98083</v>
+        <v>98090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121368982</v>
+        <v>121371841</v>
       </c>
       <c r="B7" t="n">
-        <v>105109</v>
+        <v>108989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121366035</v>
+        <v>121364323</v>
       </c>
       <c r="B8" t="n">
-        <v>98107</v>
+        <v>98778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,41 +1305,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R8" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S8" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121364323</v>
+        <v>121366971</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,25 +1408,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121371841</v>
+        <v>121368513</v>
       </c>
       <c r="B10" t="n">
-        <v>108989</v>
+        <v>99144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,20 +1511,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1535,17 +1535,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R10" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S10" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1570,12 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367308</v>
+        <v>121368982</v>
       </c>
       <c r="B12" t="n">
-        <v>98013</v>
+        <v>105109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121367305</v>
+        <v>121366035</v>
       </c>
       <c r="B2" t="n">
-        <v>98013</v>
+        <v>98107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R2" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +746,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121367308</v>
+        <v>121368982</v>
       </c>
       <c r="B3" t="n">
-        <v>98013</v>
+        <v>105109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,12 +849,12 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368514</v>
+        <v>121366702</v>
       </c>
       <c r="B4" t="n">
-        <v>99144</v>
+        <v>98090</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222662</v>
+        <v>219799</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R4" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +952,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121366035</v>
+        <v>121366971</v>
       </c>
       <c r="B5" t="n">
-        <v>98107</v>
+        <v>98083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R5" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S5" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1055,12 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121366702</v>
+        <v>121367308</v>
       </c>
       <c r="B6" t="n">
-        <v>98090</v>
+        <v>98013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,37 +1103,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>219788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R6" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121371841</v>
+        <v>121368514</v>
       </c>
       <c r="B7" t="n">
-        <v>108989</v>
+        <v>99144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,20 +1202,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121364323</v>
+        <v>121371841</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>108989</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,37 +1309,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
+          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716959</v>
+        <v>716744</v>
       </c>
       <c r="R8" t="n">
-        <v>6376779</v>
+        <v>6377151</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1364,12 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121366971</v>
+        <v>121368513</v>
       </c>
       <c r="B9" t="n">
-        <v>98083</v>
+        <v>99144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121368513</v>
+        <v>121364323</v>
       </c>
       <c r="B10" t="n">
-        <v>99144</v>
+        <v>98778</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367281</v>
+        <v>121367305</v>
       </c>
       <c r="B11" t="n">
-        <v>98015</v>
+        <v>98013</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,37 +1618,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223572</v>
+        <v>219788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>KÄRR 3850 M SO GANTHEM K:A_Norrlanda 3, Gtl</t>
+          <t>KÄRR 4300 M SO GANTHEM K:A_Norrlanda 6, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716744</v>
+        <v>716959</v>
       </c>
       <c r="R11" t="n">
-        <v>6377151</v>
+        <v>6376779</v>
       </c>
       <c r="S11" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1673,12 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121368982</v>
+        <v>121367281</v>
       </c>
       <c r="B12" t="n">
-        <v>105109</v>
+        <v>98015</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221137</v>
+        <v>223572</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,12 +1776,12 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,6 +1806,138 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125864321</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57579</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100035</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ängshök</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Circus pygargus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gardese, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>716334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6376968</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flög västerut ’i vägens riktning’</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tord Lantz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tord Lantz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>125864321</v>
       </c>
       <c r="B13" t="n">
-        <v>57579</v>
+        <v>57580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>125864321</v>
       </c>
       <c r="B13" t="n">
-        <v>57580</v>
+        <v>57584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>125864321</v>
       </c>
       <c r="B13" t="n">
-        <v>57584</v>
+        <v>57585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49418-2024 artfynd.xlsx
+++ b/artfynd/A 49418-2024 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>126944149</v>
       </c>
       <c r="B14" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>126944165</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>126944150</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>126944151</v>
       </c>
       <c r="B18" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>126944138</v>
       </c>
       <c r="B19" t="n">
-        <v>105956</v>
+        <v>106031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>126944139</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>126944164</v>
       </c>
       <c r="B21" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
